--- a/src/templates/categories.xlsx
+++ b/src/templates/categories.xlsx
@@ -17,31 +17,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="2011">
   <si>
-    <t>Company</t>
+    <t>Công ty</t>
   </si>
   <si>
     <t>WarehouseOS</t>
   </si>
   <si>
-    <t>Report</t>
+    <t>Báo cáo</t>
   </si>
   <si>
     <t>Categories</t>
   </si>
   <si>
-    <t>Exported</t>
+    <t>Ngày xuất</t>
   </si>
   <si>
     <t>18:20:13 12/09/2026 UTC+7</t>
   </si>
   <si>
-    <t>CODE</t>
-  </si>
-  <si>
-    <t>NAME</t>
-  </si>
-  <si>
-    <t>STATUS</t>
+    <t>Mã danh mục</t>
+  </si>
+  <si>
+    <t>Tên danh mục</t>
+  </si>
+  <si>
+    <t>Trạng thái</t>
   </si>
   <si>
     <t>DEMO-CAT-CE4825C6</t>
@@ -6046,19 +6046,19 @@
     <t>Long đen vênh M16 mạ điện phân</t>
   </si>
   <si>
-    <t>ĐVT</t>
-  </si>
-  <si>
-    <t>giá nhập</t>
-  </si>
-  <si>
-    <t>giá xuất</t>
-  </si>
-  <si>
-    <t>có vat hay không</t>
-  </si>
-  <si>
-    <t>vat</t>
+    <t>Đơn vị tính mặc định</t>
+  </si>
+  <si>
+    <t>Giá nhập mặc định</t>
+  </si>
+  <si>
+    <t>Giá bán mặc định</t>
+  </si>
+  <si>
+    <t>Có VAT</t>
+  </si>
+  <si>
+    <t>Thuế suất VAT (%)</t>
   </si>
 </sst>
 </file>
